--- a/academias/Lengua y Comunicación - Estadisticos 20231.xlsx
+++ b/academias/Lengua y Comunicación - Estadisticos 20231.xlsx
@@ -522,19 +522,19 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>18</v>
       </c>
       <c r="G2" s="1">
-        <v>53.8</v>
+        <v>52.6</v>
       </c>
       <c r="H2" s="1">
-        <v>46.2</v>
+        <v>47.4</v>
       </c>
       <c r="I2" s="2">
         <v>6.4</v>
@@ -554,19 +554,19 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>18</v>
       </c>
       <c r="G3" s="1">
-        <v>53.8</v>
+        <v>52.6</v>
       </c>
       <c r="H3" s="1">
-        <v>46.2</v>
+        <v>47.4</v>
       </c>
       <c r="I3" s="2">
         <v>6.4</v>
@@ -659,22 +659,22 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I6" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -694,28 +694,28 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7">
         <v>36</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>92.3</v>
+        <v>90</v>
       </c>
       <c r="H7" s="1">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="I7" s="2">
         <v>9.5</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -796,28 +796,28 @@
         <v>16</v>
       </c>
       <c r="D10">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E10">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1">
-        <v>90.7</v>
+        <v>90.3</v>
       </c>
       <c r="H10" s="1">
-        <v>9.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I10" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -898,13 +898,13 @@
         <v>26</v>
       </c>
       <c r="D13">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -916,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -968,13 +968,13 @@
         <v>28</v>
       </c>
       <c r="D15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -986,7 +986,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -1029,28 +1029,28 @@
         <v>17</v>
       </c>
       <c r="D17">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E17">
         <v>215</v>
       </c>
       <c r="F17">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G17" s="1">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="H17" s="1">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="I17" s="2">
         <v>6.2</v>
       </c>
       <c r="J17">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K17" s="1">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
     </row>
   </sheetData>
@@ -1115,13 +1115,13 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K2" s="1">
         <v>100</v>
@@ -1147,13 +1147,13 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K3" s="1">
         <v>100</v>
@@ -1252,13 +1252,13 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -1287,13 +1287,13 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -1389,13 +1389,13 @@
         <v>16</v>
       </c>
       <c r="D10">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1491,13 +1491,13 @@
         <v>26</v>
       </c>
       <c r="D13">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -1561,13 +1561,13 @@
         <v>28</v>
       </c>
       <c r="D15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -1622,13 +1622,13 @@
         <v>17</v>
       </c>
       <c r="D17">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -1708,19 +1708,19 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>18</v>
       </c>
       <c r="G2" s="1">
-        <v>53.8</v>
+        <v>52.6</v>
       </c>
       <c r="H2" s="1">
-        <v>46.2</v>
+        <v>47.4</v>
       </c>
       <c r="I2" s="2">
         <v>6.4</v>
@@ -1740,19 +1740,19 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>18</v>
       </c>
       <c r="G3" s="1">
-        <v>53.8</v>
+        <v>52.6</v>
       </c>
       <c r="H3" s="1">
-        <v>46.2</v>
+        <v>47.4</v>
       </c>
       <c r="I3" s="2">
         <v>6.4</v>
@@ -1845,22 +1845,22 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I6" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1880,28 +1880,28 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7">
         <v>36</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>92.3</v>
+        <v>90</v>
       </c>
       <c r="H7" s="1">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="I7" s="2">
         <v>9.5</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1982,28 +1982,28 @@
         <v>16</v>
       </c>
       <c r="D10">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E10">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1">
-        <v>90.7</v>
+        <v>90.3</v>
       </c>
       <c r="H10" s="1">
-        <v>9.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I10" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2084,13 +2084,13 @@
         <v>26</v>
       </c>
       <c r="D13">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -2154,13 +2154,13 @@
         <v>28</v>
       </c>
       <c r="D15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -2172,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -2215,28 +2215,28 @@
         <v>17</v>
       </c>
       <c r="D17">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E17">
         <v>215</v>
       </c>
       <c r="F17">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G17" s="1">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="H17" s="1">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="I17" s="2">
         <v>6.2</v>
       </c>
       <c r="J17">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K17" s="1">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Lengua y Comunicación - Estadisticos 20231.xlsx
+++ b/academias/Lengua y Comunicación - Estadisticos 20231.xlsx
@@ -522,19 +522,19 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>18</v>
       </c>
       <c r="G2" s="1">
-        <v>52.6</v>
+        <v>53.8</v>
       </c>
       <c r="H2" s="1">
-        <v>47.4</v>
+        <v>46.2</v>
       </c>
       <c r="I2" s="2">
         <v>6.4</v>
@@ -554,19 +554,19 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>18</v>
       </c>
       <c r="G3" s="1">
-        <v>52.6</v>
+        <v>53.8</v>
       </c>
       <c r="H3" s="1">
-        <v>47.4</v>
+        <v>46.2</v>
       </c>
       <c r="I3" s="2">
         <v>6.4</v>
@@ -659,22 +659,22 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>91.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="H6" s="1">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -796,22 +796,22 @@
         <v>16</v>
       </c>
       <c r="D10">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E10">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F10">
         <v>19</v>
       </c>
       <c r="G10" s="1">
-        <v>90.3</v>
+        <v>90.2</v>
       </c>
       <c r="H10" s="1">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I10" s="2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -901,25 +901,25 @@
         <v>39</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F13">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>2.6</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -936,25 +936,25 @@
         <v>37</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F14">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J14">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -971,25 +971,25 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>84.2</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>15.8</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J15">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1003,25 +1003,25 @@
         <v>95</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="F16">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>95.8</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>4.2</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J16">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:11">
@@ -1032,25 +1032,25 @@
         <v>364</v>
       </c>
       <c r="E17">
-        <v>215</v>
+        <v>306</v>
       </c>
       <c r="F17">
-        <v>149</v>
+        <v>58</v>
       </c>
       <c r="G17" s="1">
-        <v>59.1</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>40.9</v>
+        <v>15.9</v>
       </c>
       <c r="I17" s="2">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>26.4</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -1115,13 +1115,13 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K2" s="1">
         <v>100</v>
@@ -1147,13 +1147,13 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K3" s="1">
         <v>100</v>
@@ -1252,13 +1252,13 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -1389,13 +1389,13 @@
         <v>16</v>
       </c>
       <c r="D10">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1427,25 +1427,25 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F11">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>58.3</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>41.7</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1459,25 +1459,25 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F12">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>58.3</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>41.7</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1494,25 +1494,25 @@
         <v>39</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F13">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>79.5</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>20.5</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J13">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1529,25 +1529,25 @@
         <v>37</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F14">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J14">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1564,25 +1564,25 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>84.2</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>15.8</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J15">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1596,25 +1596,25 @@
         <v>95</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="F16">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>22.1</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J16">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:11">
@@ -1625,25 +1625,25 @@
         <v>364</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F17">
-        <v>364</v>
+        <v>269</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>26.1</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J17">
-        <v>364</v>
+        <v>233</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1708,19 +1708,19 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>18</v>
       </c>
       <c r="G2" s="1">
-        <v>52.6</v>
+        <v>53.8</v>
       </c>
       <c r="H2" s="1">
-        <v>47.4</v>
+        <v>46.2</v>
       </c>
       <c r="I2" s="2">
         <v>6.4</v>
@@ -1740,19 +1740,19 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>18</v>
       </c>
       <c r="G3" s="1">
-        <v>52.6</v>
+        <v>53.8</v>
       </c>
       <c r="H3" s="1">
-        <v>47.4</v>
+        <v>46.2</v>
       </c>
       <c r="I3" s="2">
         <v>6.4</v>
@@ -1845,22 +1845,22 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>91.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="H6" s="1">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1982,22 +1982,22 @@
         <v>16</v>
       </c>
       <c r="D10">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E10">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F10">
         <v>19</v>
       </c>
       <c r="G10" s="1">
-        <v>90.3</v>
+        <v>90.2</v>
       </c>
       <c r="H10" s="1">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I10" s="2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -2020,19 +2020,19 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F11">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G11" s="1">
-        <v>52.8</v>
+        <v>58.3</v>
       </c>
       <c r="H11" s="1">
-        <v>47.2</v>
+        <v>41.7</v>
       </c>
       <c r="I11" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2052,19 +2052,19 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F12">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G12" s="1">
-        <v>52.8</v>
+        <v>58.3</v>
       </c>
       <c r="H12" s="1">
-        <v>47.2</v>
+        <v>41.7</v>
       </c>
       <c r="I12" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2087,25 +2087,25 @@
         <v>39</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F13">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>79.5</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>20.5</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2122,25 +2122,25 @@
         <v>37</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F14">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J14">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2157,25 +2157,25 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>84.2</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>15.8</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J15">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2189,25 +2189,25 @@
         <v>95</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="F16">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>22.1</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J16">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:11">
@@ -2218,25 +2218,25 @@
         <v>364</v>
       </c>
       <c r="E17">
-        <v>215</v>
+        <v>291</v>
       </c>
       <c r="F17">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="G17" s="1">
-        <v>59.1</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>40.9</v>
+        <v>20.1</v>
       </c>
       <c r="I17" s="2">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>26.4</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Lengua y Comunicación - Estadisticos 20231.xlsx
+++ b/academias/Lengua y Comunicación - Estadisticos 20231.xlsx
@@ -1118,25 +1118,25 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>43.6</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1150,25 +1150,25 @@
         <v>39</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>43.6</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1185,25 +1185,25 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>85.2</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>14.8</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1220,25 +1220,25 @@
         <v>24</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J5">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1255,25 +1255,25 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>91.2</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J6">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1290,25 +1290,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1325,25 +1325,25 @@
         <v>39</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F8">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>5.1</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1360,25 +1360,25 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1392,25 +1392,25 @@
         <v>194</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="F10">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J10">
-        <v>194</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1625,25 +1625,25 @@
         <v>364</v>
       </c>
       <c r="E17">
-        <v>95</v>
+        <v>295</v>
       </c>
       <c r="F17">
-        <v>269</v>
+        <v>69</v>
       </c>
       <c r="G17" s="1">
-        <v>26.1</v>
+        <v>81</v>
       </c>
       <c r="H17" s="1">
-        <v>73.90000000000001</v>
+        <v>19</v>
       </c>
       <c r="I17" s="2">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="J17">
-        <v>233</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>64</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -1711,16 +1711,16 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G2" s="1">
-        <v>53.8</v>
+        <v>56.4</v>
       </c>
       <c r="H2" s="1">
-        <v>46.2</v>
+        <v>43.6</v>
       </c>
       <c r="I2" s="2">
         <v>6.4</v>
@@ -1743,16 +1743,16 @@
         <v>39</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1">
-        <v>53.8</v>
+        <v>56.4</v>
       </c>
       <c r="H3" s="1">
-        <v>46.2</v>
+        <v>43.6</v>
       </c>
       <c r="I3" s="2">
         <v>6.4</v>
@@ -1778,19 +1778,19 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>77.8</v>
+        <v>85.2</v>
       </c>
       <c r="H4" s="1">
-        <v>22.2</v>
+        <v>14.8</v>
       </c>
       <c r="I4" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1813,19 +1813,19 @@
         <v>24</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>91.7</v>
+        <v>87.5</v>
       </c>
       <c r="H5" s="1">
-        <v>8.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="I5" s="2">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1895,7 +1895,7 @@
         <v>10</v>
       </c>
       <c r="I7" s="2">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1918,19 +1918,19 @@
         <v>39</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>92.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>7.7</v>
+        <v>5.1</v>
       </c>
       <c r="I8" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1953,19 +1953,19 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1985,19 +1985,19 @@
         <v>194</v>
       </c>
       <c r="E10">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F10">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G10" s="1">
-        <v>90.2</v>
+        <v>91.8</v>
       </c>
       <c r="H10" s="1">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I10" s="2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -2218,19 +2218,19 @@
         <v>364</v>
       </c>
       <c r="E17">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F17">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G17" s="1">
-        <v>79.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="H17" s="1">
-        <v>20.1</v>
+        <v>19</v>
       </c>
       <c r="I17" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J17">
         <v>1</v>

--- a/academias/Lengua y Comunicación - Estadisticos 20231.xlsx
+++ b/academias/Lengua y Comunicación - Estadisticos 20231.xlsx
@@ -709,13 +709,13 @@
         <v>10</v>
       </c>
       <c r="I7" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -811,13 +811,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I10" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1047,10 +1047,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1302,13 +1302,13 @@
         <v>10</v>
       </c>
       <c r="I7" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1404,13 +1404,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I10" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1640,10 +1640,10 @@
         <v>7.4</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1895,13 +1895,13 @@
         <v>10</v>
       </c>
       <c r="I7" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2000,10 +2000,10 @@
         <v>8.6</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2233,10 +2233,10 @@
         <v>7.9</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Lengua y Comunicación - Estadisticos 20231.xlsx
+++ b/academias/Lengua y Comunicación - Estadisticos 20231.xlsx
@@ -1711,19 +1711,19 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>56.4</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>43.6</v>
+        <v>17.9</v>
       </c>
       <c r="I2" s="2">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1743,19 +1743,19 @@
         <v>39</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>56.4</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>43.6</v>
+        <v>17.9</v>
       </c>
       <c r="I3" s="2">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1778,19 +1778,19 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>85.2</v>
+        <v>77.8</v>
       </c>
       <c r="H4" s="1">
-        <v>14.8</v>
+        <v>22.2</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1813,19 +1813,19 @@
         <v>24</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="H5" s="1">
-        <v>12.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1883,19 +1883,19 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H7" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I7" s="2">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>5.1</v>
       </c>
       <c r="I8" s="2">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1953,19 +1953,19 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I9" s="2">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1997,7 +1997,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I10" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2087,19 +2087,19 @@
         <v>39</v>
       </c>
       <c r="E13">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>79.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>20.5</v>
+        <v>17.9</v>
       </c>
       <c r="I13" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2122,19 +2122,19 @@
         <v>37</v>
       </c>
       <c r="E14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1">
-        <v>73</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>27</v>
+        <v>21.6</v>
       </c>
       <c r="I14" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>15.8</v>
       </c>
       <c r="I15" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2189,19 +2189,19 @@
         <v>95</v>
       </c>
       <c r="E16">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F16">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G16" s="1">
-        <v>77.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>22.1</v>
+        <v>18.9</v>
       </c>
       <c r="I16" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2218,19 +2218,19 @@
         <v>364</v>
       </c>
       <c r="E17">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="F17">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G17" s="1">
-        <v>81</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>19</v>
+        <v>15.4</v>
       </c>
       <c r="I17" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J17">
         <v>0</v>

--- a/academias/Lengua y Comunicación - Estadisticos 20231.xlsx
+++ b/academias/Lengua y Comunicación - Estadisticos 20231.xlsx
@@ -2020,19 +2020,19 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F11">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1">
-        <v>58.3</v>
+        <v>72.2</v>
       </c>
       <c r="H11" s="1">
-        <v>41.7</v>
+        <v>27.8</v>
       </c>
       <c r="I11" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2052,19 +2052,19 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F12">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>58.3</v>
+        <v>72.2</v>
       </c>
       <c r="H12" s="1">
-        <v>41.7</v>
+        <v>27.8</v>
       </c>
       <c r="I12" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2218,16 +2218,16 @@
         <v>364</v>
       </c>
       <c r="E17">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F17">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G17" s="1">
-        <v>84.59999999999999</v>
+        <v>86</v>
       </c>
       <c r="H17" s="1">
-        <v>15.4</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2">
         <v>7.6</v>

--- a/academias/Lengua y Comunicación - Estadisticos 20231.xlsx
+++ b/academias/Lengua y Comunicación - Estadisticos 20231.xlsx
@@ -1723,7 +1723,7 @@
         <v>17.9</v>
       </c>
       <c r="I2" s="2">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1755,7 +1755,7 @@
         <v>17.9</v>
       </c>
       <c r="I3" s="2">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>22.2</v>
       </c>
       <c r="I4" s="2">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1895,7 +1895,7 @@
         <v>5</v>
       </c>
       <c r="I7" s="2">
-        <v>8.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>5.1</v>
       </c>
       <c r="I8" s="2">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>3.3</v>
       </c>
       <c r="I9" s="2">
-        <v>7.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1997,7 +1997,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I10" s="2">
-        <v>8.1</v>
+        <v>9.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2032,7 +2032,7 @@
         <v>27.8</v>
       </c>
       <c r="I11" s="2">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2064,7 +2064,7 @@
         <v>27.8</v>
       </c>
       <c r="I12" s="2">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2099,7 +2099,7 @@
         <v>17.9</v>
       </c>
       <c r="I13" s="2">
-        <v>6.9</v>
+        <v>9.1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2134,7 +2134,7 @@
         <v>21.6</v>
       </c>
       <c r="I14" s="2">
-        <v>7</v>
+        <v>8.9</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>15.8</v>
       </c>
       <c r="I15" s="2">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2201,7 +2201,7 @@
         <v>18.9</v>
       </c>
       <c r="I16" s="2">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>14</v>
       </c>
       <c r="I17" s="2">
-        <v>7.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>

--- a/academias/Lengua y Comunicación - Estadisticos 20231.xlsx
+++ b/academias/Lengua y Comunicación - Estadisticos 20231.xlsx
@@ -1723,7 +1723,7 @@
         <v>17.9</v>
       </c>
       <c r="I2" s="2">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1755,7 +1755,7 @@
         <v>17.9</v>
       </c>
       <c r="I3" s="2">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>22.2</v>
       </c>
       <c r="I4" s="2">
-        <v>8.9</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I6" s="2">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1895,7 +1895,7 @@
         <v>5</v>
       </c>
       <c r="I7" s="2">
-        <v>9.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>5.1</v>
       </c>
       <c r="I8" s="2">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>3.3</v>
       </c>
       <c r="I9" s="2">
-        <v>9.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1997,7 +1997,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I10" s="2">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2032,7 +2032,7 @@
         <v>27.8</v>
       </c>
       <c r="I11" s="2">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2064,7 +2064,7 @@
         <v>27.8</v>
       </c>
       <c r="I12" s="2">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2099,7 +2099,7 @@
         <v>17.9</v>
       </c>
       <c r="I13" s="2">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2134,7 +2134,7 @@
         <v>21.6</v>
       </c>
       <c r="I14" s="2">
-        <v>8.9</v>
+        <v>7</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>15.8</v>
       </c>
       <c r="I15" s="2">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2201,7 +2201,7 @@
         <v>18.9</v>
       </c>
       <c r="I16" s="2">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>14</v>
       </c>
       <c r="I17" s="2">
-        <v>9.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J17">
         <v>0</v>
